--- a/data/trans_camb/IQ26A_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IQ26A_R2-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-3,27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,56</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,97</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,39</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>10,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>4,35</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 6,13</t>
+          <t>-9,63; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 6,59</t>
+          <t>-5,88; 9,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 24,93</t>
+          <t>-9,34; 12,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 5,63</t>
+          <t>-11,48; 4,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 10,11</t>
+          <t>-11,22; 5,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 10,81</t>
+          <t>-4,24; 25,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 2,49</t>
+          <t>-8,12; 2,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 5,63</t>
+          <t>-5,76; 5,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 12,9</t>
+          <t>-4,12; 13,67</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-20,81%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-2,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-21,78%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-17,04%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-20,81%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,58%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,17%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,88; 63,05</t>
+          <t>-63,24; 74,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,42; 69,36</t>
+          <t>-41,14; 123,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 214,97</t>
+          <t>-68,66; 143,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 71,39</t>
+          <t>-61,07; 43,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 136,53</t>
+          <t>-60,4; 52,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,97; 147,01</t>
+          <t>-27,97; 205,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,7; 24,25</t>
+          <t>-52,0; 28,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 52,1</t>
+          <t>-37,29; 55,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 113,48</t>
+          <t>-27,87; 123,0</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,94</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-4,49</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,71</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,94</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>12,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>9,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 3,08</t>
+          <t>-13,61; 2,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 9,05</t>
+          <t>-6,56; 9,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 27,95</t>
+          <t>-8,91; 25,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 1,35</t>
+          <t>-12,89; 2,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 9,71</t>
+          <t>-8,03; 8,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 25,02</t>
+          <t>-3,12; 28,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 0,24</t>
+          <t>-11,1; 0,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 6,29</t>
+          <t>-5,49; 6,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 20,24</t>
+          <t>-0,62; 21,37</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-40,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40,87%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-31,28%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85,78%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-40,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-66,03; 37,88</t>
+          <t>-73,3; 20,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 102,0</t>
+          <t>-37,52; 93,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 255,77</t>
+          <t>-53,3; 240,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 15,78</t>
+          <t>-68,52; 31,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,35; 94,71</t>
+          <t>-42,04; 87,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,0; 229,14</t>
+          <t>-19,09; 258,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,72; 3,61</t>
+          <t>-61,26; 1,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 53,88</t>
+          <t>-30,18; 58,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 170,13</t>
+          <t>-4,03; 166,35</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,77</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,88</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,49</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,72</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>20,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,77</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,1</t>
+          <t>18,69</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,26</t>
+          <t>12,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 13,7</t>
+          <t>-5,17; 7,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 6,84</t>
+          <t>-0,92; 15,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 52,6</t>
+          <t>-3,92; 26,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 7,56</t>
+          <t>-2,8; 13,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 15,23</t>
+          <t>-8,57; 6,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 28,94</t>
+          <t>1,13; 43,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 8,58</t>
+          <t>-2,01; 8,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 9,07</t>
+          <t>-1,65; 9,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 28,55</t>
+          <t>1,46; 28,46</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>92,65%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>107,91%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>62,05%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-8,19%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>232,78%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>110,93%</t>
+          <t>211,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>167,39%</t>
+          <t>158,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 274,84</t>
+          <t>-56,22; 162,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 147,06</t>
+          <t>-15,61; 356,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 811,95</t>
+          <t>-52,09; 626,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,66; 170,73</t>
+          <t>-23,51; 319,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 354,0</t>
+          <t>-70,97; 129,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,84; 669,57</t>
+          <t>-12,51; 921,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 137,92</t>
+          <t>-19,43; 159,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 153,54</t>
+          <t>-18,8; 166,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,26; 471,3</t>
+          <t>7,59; 437,83</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,06</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,77</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,51</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,54</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,06</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>7,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>5,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 3,22</t>
+          <t>-4,01; 6,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 7,03</t>
+          <t>-1,05; 9,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 29,03</t>
+          <t>-4,62; 17,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 5,65</t>
+          <t>-7,31; 2,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 9,38</t>
+          <t>-3,59; 7,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 16,1</t>
+          <t>-4,01; 21,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 3,08</t>
+          <t>-4,49; 2,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 6,86</t>
+          <t>-1,18; 6,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 19,24</t>
+          <t>-1,6; 14,34</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>36,86%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>43,35%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-18,5%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>11,59%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>81,12%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>36,86%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,5; 29,52</t>
+          <t>-30,89; 68,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 64,49</t>
+          <t>-8,69; 115,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 296,07</t>
+          <t>-42,16; 186,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 66,73</t>
+          <t>-48,08; 30,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 107,68</t>
+          <t>-24,64; 74,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 170,6</t>
+          <t>-30,0; 191,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 30,82</t>
+          <t>-32,29; 26,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 67,24</t>
+          <t>-8,51; 64,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 170,23</t>
+          <t>-14,25; 131,85</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,04</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4,22</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>22,62</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-5,48</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9,74</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,04</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,22</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,67</t>
+          <t>11,31</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17,23</t>
+          <t>18,6</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 0,46</t>
+          <t>-3,42; 9,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 5,5</t>
+          <t>-2,53; 11,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 25,32</t>
+          <t>8,66; 37,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 9,4</t>
+          <t>-11,95; 0,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 11,29</t>
+          <t>-7,91; 6,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,41; 39,47</t>
+          <t>-1,68; 30,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,24</t>
+          <t>-5,99; 3,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 6,12</t>
+          <t>-3,24; 6,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,08; 28,3</t>
+          <t>7,98; 30,81</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>39,53%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>212,14%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-42,94%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-7,82%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>76,36%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>39,53%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>203,23%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>148,57%</t>
+          <t>160,3%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,59; 7,73</t>
+          <t>-28,9; 115,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,78; 63,59</t>
+          <t>-18,89; 151,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 260,32</t>
+          <t>66,69; 489,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 115,24</t>
+          <t>-68,28; 20,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 153,06</t>
+          <t>-47,73; 68,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,01; 455,77</t>
+          <t>-11,76; 292,06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,01; 36,69</t>
+          <t>-42,17; 34,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 64,61</t>
+          <t>-22,63; 69,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>47,78; 292,94</t>
+          <t>55,11; 300,67</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-11,23</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-9,77</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-8,86</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-11,27</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>6,78</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-11,23</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-9,77</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-11,07</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,75</t>
+          <t>-4,43</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-20,1; -1,96</t>
+          <t>-21,73; -0,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 18,99</t>
+          <t>-19,3; 0,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 29,01</t>
+          <t>-21,82; 10,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-21,48; -1,5</t>
+          <t>-20,98; -2,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 1,19</t>
+          <t>-5,99; 18,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 5,37</t>
+          <t>-15,46; 28,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-17,55; -3,73</t>
+          <t>-18,14; -4,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 5,68</t>
+          <t>-9,57; 6,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 7,1</t>
+          <t>-15,45; 8,98</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-50,27%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-43,76%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-39,69%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-62,01%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>37,31%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-50,27%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-43,76%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-49,56%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-28,51%</t>
+          <t>-21,92%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-86,75; -6,33</t>
+          <t>-76,5; 0,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 140,67</t>
+          <t>-71,36; 9,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,62; 188,53</t>
+          <t>-85,0; 67,25</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-74,32; -3,44</t>
+          <t>-90,26; -0,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-73,64; 10,12</t>
+          <t>-25,31; 144,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-87,1; 39,72</t>
+          <t>-76,57; 191,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-74,36; -21,37</t>
+          <t>-76,53; -23,5</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 36,04</t>
+          <t>-39,66; 40,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-67,62; 42,47</t>
+          <t>-67,82; 54,66</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,22</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2,58</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6,89</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-3,55</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,49</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>10,75</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>10,1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,97</t>
+          <t>8,22</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -0,76</t>
+          <t>-4,08; 1,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,61</t>
+          <t>-0,42; 5,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,53; 18,57</t>
+          <t>1,69; 12,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 1,63</t>
+          <t>-6,59; -0,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,32</t>
+          <t>-2,45; 3,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,07; 11,68</t>
+          <t>4,09; 16,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,3</t>
+          <t>-4,41; -0,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,82</t>
+          <t>-0,66; 3,77</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,85; 12,42</t>
+          <t>4,33; 12,59</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-10,1%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>56,96%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-25,98%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>78,79%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-10,1%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>21,32%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-43,36; -5,83</t>
+          <t>-30,48; 14,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 29,85</t>
+          <t>-3,35; 52,05</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31,33; 149,07</t>
+          <t>14,25; 111,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 14,61</t>
+          <t>-42,62; -4,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 50,08</t>
+          <t>-16,42; 31,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,1; 107,63</t>
+          <t>26,98; 133,79</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,41; -2,97</t>
+          <t>-31,71; -3,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 32,29</t>
+          <t>-4,77; 32,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>27,57; 102,91</t>
+          <t>32,55; 104,59</t>
         </is>
       </c>
     </row>
